--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D2">
-        <v>243</v>
+        <v>373</v>
       </c>
       <c r="E2">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>297</v>
+        <v>395</v>
       </c>
       <c r="E3">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -453,13 +453,13 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>426</v>
